--- a/templates/10-value-stream-map.xlsx
+++ b/templates/10-value-stream-map.xlsx
@@ -671,15 +671,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B16"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="29" min="1" max="1"/>
     <col width="108" customWidth="1" style="29" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="30" customHeight="1" s="30">
       <c r="B2" s="31" t="inlineStr">
         <is>
@@ -694,6 +695,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="30">
       <c r="B5" s="33" t="inlineStr">
         <is>
@@ -736,6 +738,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12" ht="24" customHeight="1" s="30">
       <c r="B12" s="33" t="inlineStr">
         <is>
@@ -757,6 +760,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16" ht="25.5" customHeight="1" s="30">
       <c r="B16" s="35" t="inlineStr">
         <is>
@@ -764,10 +768,34 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -775,7 +803,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
@@ -1461,8 +1489,8 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
--- a/templates/10-value-stream-map.xlsx
+++ b/templates/10-value-stream-map.xlsx
@@ -490,6 +490,165 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <roundedCorners val="0"/>
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Where the time actually goes, step by step</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Touch time</v>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="3F8F5A"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Value stream'!$B$10:$B$29</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Value stream'!$E$10:$E$29</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Waiting</v>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="C0392B"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Value stream'!$B$10:$B$29</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Value stream'!$F$10:$F$29</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <overlap val="100"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="3"/>
+        <tickMarkSkip val="3"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Minutes</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7920000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1492,5 +1651,6 @@
   <printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/templates/10-value-stream-map.xlsx
+++ b/templates/10-value-stream-map.xlsx
@@ -160,7 +160,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -209,6 +209,11 @@
         <bgColor rgb="FF1F2937"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECFAEF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -244,7 +249,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -419,6 +424,21 @@
     </xf>
     <xf numFmtId="165" fontId="16" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="15" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -532,12 +552,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Value stream'!$B$10:$B$29</f>
+              <f>'Value stream'!$B$10:$B$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Value stream'!$E$10:$E$29</f>
+              <f>'Value stream'!$E$10:$E$28</f>
             </numRef>
           </val>
         </ser>
@@ -557,12 +577,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Value stream'!$B$10:$B$29</f>
+              <f>'Value stream'!$B$10:$B$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Value stream'!$F$10:$F$29</f>
+              <f>'Value stream'!$F$10:$F$28</f>
             </numRef>
           </val>
         </ser>
@@ -967,12 +987,16 @@
   <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="32" customWidth="1" style="29" min="1" max="1"/>
-    <col width="12" customWidth="1" style="29" min="2" max="2"/>
+    <col width="5" customWidth="1" style="29" min="1" max="1"/>
+    <col width="34" customWidth="1" style="29" min="2" max="2"/>
     <col width="15" customWidth="1" style="29" min="3" max="3"/>
-    <col width="18" customWidth="1" style="29" min="4" max="4"/>
-    <col width="44" customWidth="1" style="29" min="5" max="5"/>
-    <col width="4" customWidth="1" style="29" min="6" max="10"/>
+    <col width="22" customWidth="1" style="29" min="4" max="4"/>
+    <col width="13" customWidth="1" style="29" min="5" max="5"/>
+    <col width="15" customWidth="1" style="29" min="6" max="10"/>
+    <col width="13" customWidth="1" style="30" min="7" max="7"/>
+    <col width="15" customWidth="1" style="30" min="8" max="8"/>
+    <col width="11" customWidth="1" style="30" min="9" max="9"/>
+    <col width="34" customWidth="1" style="30" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1" s="30">
@@ -1085,160 +1109,392 @@
       </c>
     </row>
     <row r="10" ht="113.4" customHeight="1" s="30">
-      <c r="A10" s="44" t="n">
+      <c r="A10" s="59" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="44" t="inlineStr">
+      <c r="B10" s="59" t="inlineStr">
         <is>
           <t>Customer submits the form</t>
         </is>
       </c>
-      <c r="C10" s="44" t="inlineStr">
+      <c r="C10" s="59" t="inlineStr">
         <is>
           <t>Customer</t>
         </is>
       </c>
-      <c r="D10" s="44" t="inlineStr">
+      <c r="D10" s="59" t="inlineStr">
         <is>
           <t>Help centre</t>
         </is>
       </c>
-      <c r="E10" s="44" t="n">
+      <c r="E10" s="59" t="n">
         <v>2</v>
       </c>
-      <c r="F10" s="44" t="n">
+      <c r="F10" s="59" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="45" t="n">
+      <c r="G10" s="60" t="n">
         <v>0.92</v>
       </c>
-      <c r="H10" s="44" t="inlineStr">
+      <c r="H10" s="59" t="inlineStr">
         <is>
           <t>Value-add</t>
         </is>
       </c>
-      <c r="I10" s="44" t="inlineStr">
+      <c r="I10" s="59" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J10" s="44" t="inlineStr">
+      <c r="J10" s="59" t="inlineStr">
         <is>
           <t>Form has 3 fields nobody reads</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" s="30">
-      <c r="A11" s="46" t="n">
+      <c r="A11" s="61" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="47" t="n"/>
-      <c r="C11" s="47" t="n"/>
-      <c r="D11" s="47" t="n"/>
-      <c r="E11" s="47" t="n"/>
-      <c r="F11" s="47" t="n"/>
-      <c r="G11" s="48" t="n"/>
-      <c r="H11" s="47" t="n"/>
-      <c r="I11" s="47" t="n"/>
-      <c r="J11" s="47" t="n"/>
+      <c r="B11" s="62" t="inlineStr">
+        <is>
+          <t>Sits in the unassigned queue</t>
+        </is>
+      </c>
+      <c r="C11" s="62" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" s="62" t="inlineStr">
+        <is>
+          <t>Zendesk</t>
+        </is>
+      </c>
+      <c r="E11" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="62" t="n">
+        <v>240</v>
+      </c>
+      <c r="G11" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="62" t="inlineStr">
+        <is>
+          <t>Non-value-add</t>
+        </is>
+      </c>
+      <c r="I11" s="62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J11" s="62" t="inlineStr">
+        <is>
+          <t>Overnight arrivals wait until the morning shift</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="30" customHeight="1" s="30">
-      <c r="A12" s="46" t="n">
+      <c r="A12" s="61" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="47" t="n"/>
-      <c r="C12" s="47" t="n"/>
-      <c r="D12" s="47" t="n"/>
-      <c r="E12" s="47" t="n"/>
-      <c r="F12" s="47" t="n"/>
-      <c r="G12" s="48" t="n"/>
-      <c r="H12" s="47" t="n"/>
-      <c r="I12" s="47" t="n"/>
-      <c r="J12" s="47" t="n"/>
+      <c r="B12" s="62" t="inlineStr">
+        <is>
+          <t>Tier 1 triage and tagging</t>
+        </is>
+      </c>
+      <c r="C12" s="62" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="D12" s="62" t="inlineStr">
+        <is>
+          <t>Zendesk</t>
+        </is>
+      </c>
+      <c r="E12" s="62" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="63" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H12" s="62" t="inlineStr">
+        <is>
+          <t>Business-value-add</t>
+        </is>
+      </c>
+      <c r="I12" s="62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J12" s="62" t="inlineStr">
+        <is>
+          <t>22% get the wrong contact reason, which breaks routing</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="30" customHeight="1" s="30">
-      <c r="A13" s="46" t="n">
+      <c r="A13" s="61" t="n">
         <v>4</v>
       </c>
-      <c r="B13" s="47" t="n"/>
-      <c r="C13" s="47" t="n"/>
-      <c r="D13" s="47" t="n"/>
-      <c r="E13" s="47" t="n"/>
-      <c r="F13" s="47" t="n"/>
-      <c r="G13" s="48" t="n"/>
-      <c r="H13" s="47" t="n"/>
-      <c r="I13" s="47" t="n"/>
-      <c r="J13" s="47" t="n"/>
+      <c r="B13" s="62" t="inlineStr">
+        <is>
+          <t>Waits for the daily Billing Ops sweep</t>
+        </is>
+      </c>
+      <c r="C13" s="62" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D13" s="62" t="inlineStr">
+        <is>
+          <t>Zendesk</t>
+        </is>
+      </c>
+      <c r="E13" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="62" t="n">
+        <v>480</v>
+      </c>
+      <c r="G13" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="62" t="inlineStr">
+        <is>
+          <t>Non-value-add</t>
+        </is>
+      </c>
+      <c r="I13" s="62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J13" s="62" t="inlineStr">
+        <is>
+          <t>Billing Ops pull the queue once a day at 10:00</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="30" customHeight="1" s="30">
-      <c r="A14" s="46" t="n">
+      <c r="A14" s="61" t="n">
         <v>5</v>
       </c>
-      <c r="B14" s="47" t="n"/>
-      <c r="C14" s="47" t="n"/>
-      <c r="D14" s="47" t="n"/>
-      <c r="E14" s="47" t="n"/>
-      <c r="F14" s="47" t="n"/>
-      <c r="G14" s="48" t="n"/>
-      <c r="H14" s="47" t="n"/>
-      <c r="I14" s="47" t="n"/>
-      <c r="J14" s="47" t="n"/>
+      <c r="B14" s="62" t="inlineStr">
+        <is>
+          <t>Billing Ops checks the posting</t>
+        </is>
+      </c>
+      <c r="C14" s="62" t="inlineStr">
+        <is>
+          <t>Billing Ops</t>
+        </is>
+      </c>
+      <c r="D14" s="62" t="inlineStr">
+        <is>
+          <t>Billing console + warehouse</t>
+        </is>
+      </c>
+      <c r="E14" s="62" t="n">
+        <v>11</v>
+      </c>
+      <c r="F14" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="63" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H14" s="62" t="inlineStr">
+        <is>
+          <t>Value-add</t>
+        </is>
+      </c>
+      <c r="I14" s="62" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J14" s="62" t="inlineStr">
+        <is>
+          <t>15% bounce back to Tier 1 for missing evidence</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="30" customHeight="1" s="30">
-      <c r="A15" s="46" t="n">
+      <c r="A15" s="61" t="n">
         <v>6</v>
       </c>
-      <c r="B15" s="47" t="n"/>
-      <c r="C15" s="47" t="n"/>
-      <c r="D15" s="47" t="n"/>
-      <c r="E15" s="47" t="n"/>
-      <c r="F15" s="47" t="n"/>
-      <c r="G15" s="48" t="n"/>
-      <c r="H15" s="47" t="n"/>
-      <c r="I15" s="47" t="n"/>
-      <c r="J15" s="47" t="n"/>
+      <c r="B15" s="62" t="inlineStr">
+        <is>
+          <t>Waits for the nightly adjustment batch</t>
+        </is>
+      </c>
+      <c r="C15" s="62" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D15" s="62" t="inlineStr">
+        <is>
+          <t>Billing platform</t>
+        </is>
+      </c>
+      <c r="E15" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="62" t="n">
+        <v>720</v>
+      </c>
+      <c r="G15" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="62" t="inlineStr">
+        <is>
+          <t>Non-value-add</t>
+        </is>
+      </c>
+      <c r="I15" s="62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J15" s="62" t="inlineStr">
+        <is>
+          <t>Cut-off is 18:00; miss it and you wait another day</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="30" customHeight="1" s="30">
-      <c r="A16" s="46" t="n">
+      <c r="A16" s="61" t="n">
         <v>7</v>
       </c>
-      <c r="B16" s="47" t="n"/>
-      <c r="C16" s="47" t="n"/>
-      <c r="D16" s="47" t="n"/>
-      <c r="E16" s="47" t="n"/>
-      <c r="F16" s="47" t="n"/>
-      <c r="G16" s="48" t="n"/>
-      <c r="H16" s="47" t="n"/>
-      <c r="I16" s="47" t="n"/>
-      <c r="J16" s="47" t="n"/>
+      <c r="B16" s="62" t="inlineStr">
+        <is>
+          <t>Adjustment posts, agent verifies</t>
+        </is>
+      </c>
+      <c r="C16" s="62" t="inlineStr">
+        <is>
+          <t>Billing Ops</t>
+        </is>
+      </c>
+      <c r="D16" s="62" t="inlineStr">
+        <is>
+          <t>Billing console</t>
+        </is>
+      </c>
+      <c r="E16" s="62" t="n">
+        <v>6</v>
+      </c>
+      <c r="F16" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="63" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H16" s="62" t="inlineStr">
+        <is>
+          <t>Value-add</t>
+        </is>
+      </c>
+      <c r="I16" s="62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J16" s="62" t="inlineStr"/>
     </row>
     <row r="17" ht="30" customHeight="1" s="30">
-      <c r="A17" s="46" t="n">
+      <c r="A17" s="61" t="n">
         <v>8</v>
       </c>
-      <c r="B17" s="47" t="n"/>
-      <c r="C17" s="47" t="n"/>
-      <c r="D17" s="47" t="n"/>
-      <c r="E17" s="47" t="n"/>
-      <c r="F17" s="47" t="n"/>
-      <c r="G17" s="48" t="n"/>
-      <c r="H17" s="47" t="n"/>
-      <c r="I17" s="47" t="n"/>
-      <c r="J17" s="47" t="n"/>
+      <c r="B17" s="62" t="inlineStr">
+        <is>
+          <t>Waits for the customer to confirm</t>
+        </is>
+      </c>
+      <c r="C17" s="62" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="D17" s="62" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E17" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="62" t="n">
+        <v>960</v>
+      </c>
+      <c r="G17" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="62" t="inlineStr">
+        <is>
+          <t>Non-value-add</t>
+        </is>
+      </c>
+      <c r="I17" s="62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J17" s="62" t="inlineStr">
+        <is>
+          <t>Nothing chases the customer; this is the longest single wait</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="30" customHeight="1" s="30">
-      <c r="A18" s="46" t="n">
+      <c r="A18" s="61" t="n">
         <v>9</v>
       </c>
-      <c r="B18" s="47" t="n"/>
-      <c r="C18" s="47" t="n"/>
-      <c r="D18" s="47" t="n"/>
-      <c r="E18" s="47" t="n"/>
-      <c r="F18" s="47" t="n"/>
-      <c r="G18" s="48" t="n"/>
-      <c r="H18" s="47" t="n"/>
-      <c r="I18" s="47" t="n"/>
-      <c r="J18" s="47" t="n"/>
+      <c r="B18" s="62" t="inlineStr">
+        <is>
+          <t>Agent closes and confirms</t>
+        </is>
+      </c>
+      <c r="C18" s="62" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="D18" s="62" t="inlineStr">
+        <is>
+          <t>Zendesk</t>
+        </is>
+      </c>
+      <c r="E18" s="62" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="63" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="H18" s="62" t="inlineStr">
+        <is>
+          <t>Value-add</t>
+        </is>
+      </c>
+      <c r="I18" s="62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J18" s="62" t="inlineStr"/>
     </row>
     <row r="19" ht="30" customHeight="1" s="30">
       <c r="A19" s="46" t="n">

--- a/templates/10-value-stream-map.xlsx
+++ b/templates/10-value-stream-map.xlsx
@@ -550,6 +550,7 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="0"/>
           <cat>
             <numRef>
               <f>'Value stream'!$B$10:$B$28</f>
@@ -575,6 +576,7 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="0"/>
           <cat>
             <numRef>
               <f>'Value stream'!$B$10:$B$28</f>

--- a/templates/10-value-stream-map.xlsx
+++ b/templates/10-value-stream-map.xlsx
@@ -21,7 +21,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -159,8 +159,12 @@
       <color rgb="FFB45309"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -214,6 +218,11 @@
         <fgColor rgb="FFECFAEF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F7FF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -249,7 +258,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -440,6 +449,8 @@
     <xf numFmtId="9" fontId="15" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -593,6 +604,40 @@
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <v>Average wait per step</v>
+          </tx>
+          <spPr>
+            <a:ln w="18000">
+              <a:solidFill>
+                <a:srgbClr val="C0392B"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'Value stream'!$L$10:$L$28</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
       <catAx>
         <axId val="10"/>
         <scaling>
@@ -638,7 +683,7 @@
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="r"/>
+      <legendPos val="b"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -650,7 +695,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>11</col>
+      <col>13</col>
       <colOff>0</colOff>
       <row>8</row>
       <rowOff>0</rowOff>
@@ -986,7 +1031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:L49"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -1109,6 +1154,11 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="L9" s="64" t="inlineStr">
+        <is>
+          <t>Average wait</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="113.4" customHeight="1" s="30">
       <c r="A10" s="59" t="n">
@@ -1153,6 +1203,10 @@
           <t>Form has 3 fields nobody reads</t>
         </is>
       </c>
+      <c r="L10" s="65">
+        <f>IF(B10="","",AVERAGE($F$10:$F$28))</f>
+        <v/>
+      </c>
     </row>
     <row r="11" ht="30" customHeight="1" s="30">
       <c r="A11" s="61" t="n">
@@ -1197,6 +1251,10 @@
           <t>Overnight arrivals wait until the morning shift</t>
         </is>
       </c>
+      <c r="L11" s="65">
+        <f>IF(B11="","",AVERAGE($F$10:$F$28))</f>
+        <v/>
+      </c>
     </row>
     <row r="12" ht="30" customHeight="1" s="30">
       <c r="A12" s="61" t="n">
@@ -1241,6 +1299,10 @@
           <t>22% get the wrong contact reason, which breaks routing</t>
         </is>
       </c>
+      <c r="L12" s="65">
+        <f>IF(B12="","",AVERAGE($F$10:$F$28))</f>
+        <v/>
+      </c>
     </row>
     <row r="13" ht="30" customHeight="1" s="30">
       <c r="A13" s="61" t="n">
@@ -1285,6 +1347,10 @@
           <t>Billing Ops pull the queue once a day at 10:00</t>
         </is>
       </c>
+      <c r="L13" s="65">
+        <f>IF(B13="","",AVERAGE($F$10:$F$28))</f>
+        <v/>
+      </c>
     </row>
     <row r="14" ht="30" customHeight="1" s="30">
       <c r="A14" s="61" t="n">
@@ -1329,6 +1395,10 @@
           <t>15% bounce back to Tier 1 for missing evidence</t>
         </is>
       </c>
+      <c r="L14" s="65">
+        <f>IF(B14="","",AVERAGE($F$10:$F$28))</f>
+        <v/>
+      </c>
     </row>
     <row r="15" ht="30" customHeight="1" s="30">
       <c r="A15" s="61" t="n">
@@ -1373,6 +1443,10 @@
           <t>Cut-off is 18:00; miss it and you wait another day</t>
         </is>
       </c>
+      <c r="L15" s="65">
+        <f>IF(B15="","",AVERAGE($F$10:$F$28))</f>
+        <v/>
+      </c>
     </row>
     <row r="16" ht="30" customHeight="1" s="30">
       <c r="A16" s="61" t="n">
@@ -1413,6 +1487,10 @@
         </is>
       </c>
       <c r="J16" s="62" t="inlineStr"/>
+      <c r="L16" s="65">
+        <f>IF(B16="","",AVERAGE($F$10:$F$28))</f>
+        <v/>
+      </c>
     </row>
     <row r="17" ht="30" customHeight="1" s="30">
       <c r="A17" s="61" t="n">
@@ -1457,6 +1535,10 @@
           <t>Nothing chases the customer; this is the longest single wait</t>
         </is>
       </c>
+      <c r="L17" s="65">
+        <f>IF(B17="","",AVERAGE($F$10:$F$28))</f>
+        <v/>
+      </c>
     </row>
     <row r="18" ht="30" customHeight="1" s="30">
       <c r="A18" s="61" t="n">
@@ -1497,6 +1579,10 @@
         </is>
       </c>
       <c r="J18" s="62" t="inlineStr"/>
+      <c r="L18" s="65">
+        <f>IF(B18="","",AVERAGE($F$10:$F$28))</f>
+        <v/>
+      </c>
     </row>
     <row r="19" ht="30" customHeight="1" s="30">
       <c r="A19" s="46" t="n">
@@ -1511,6 +1597,10 @@
       <c r="H19" s="47" t="n"/>
       <c r="I19" s="47" t="n"/>
       <c r="J19" s="47" t="n"/>
+      <c r="L19" s="65">
+        <f>IF(B19="","",AVERAGE($F$10:$F$28))</f>
+        <v/>
+      </c>
     </row>
     <row r="20" ht="30" customHeight="1" s="30">
       <c r="A20" s="46" t="n">
@@ -1525,6 +1615,10 @@
       <c r="H20" s="47" t="n"/>
       <c r="I20" s="47" t="n"/>
       <c r="J20" s="47" t="n"/>
+      <c r="L20" s="65">
+        <f>IF(B20="","",AVERAGE($F$10:$F$28))</f>
+        <v/>
+      </c>
     </row>
     <row r="21" ht="30" customHeight="1" s="30">
       <c r="A21" s="46" t="n">
@@ -1539,6 +1633,10 @@
       <c r="H21" s="47" t="n"/>
       <c r="I21" s="47" t="n"/>
       <c r="J21" s="47" t="n"/>
+      <c r="L21" s="65">
+        <f>IF(B21="","",AVERAGE($F$10:$F$28))</f>
+        <v/>
+      </c>
     </row>
     <row r="22" ht="30" customHeight="1" s="30">
       <c r="A22" s="46" t="n">
@@ -1553,6 +1651,10 @@
       <c r="H22" s="47" t="n"/>
       <c r="I22" s="47" t="n"/>
       <c r="J22" s="47" t="n"/>
+      <c r="L22" s="65">
+        <f>IF(B22="","",AVERAGE($F$10:$F$28))</f>
+        <v/>
+      </c>
     </row>
     <row r="23" ht="30" customHeight="1" s="30">
       <c r="A23" s="46" t="n">
@@ -1567,6 +1669,10 @@
       <c r="H23" s="47" t="n"/>
       <c r="I23" s="47" t="n"/>
       <c r="J23" s="47" t="n"/>
+      <c r="L23" s="65">
+        <f>IF(B23="","",AVERAGE($F$10:$F$28))</f>
+        <v/>
+      </c>
     </row>
     <row r="24" ht="30" customHeight="1" s="30">
       <c r="A24" s="46" t="n">
@@ -1581,6 +1687,10 @@
       <c r="H24" s="47" t="n"/>
       <c r="I24" s="47" t="n"/>
       <c r="J24" s="47" t="n"/>
+      <c r="L24" s="65">
+        <f>IF(B24="","",AVERAGE($F$10:$F$28))</f>
+        <v/>
+      </c>
     </row>
     <row r="25" ht="30" customHeight="1" s="30">
       <c r="A25" s="46" t="n">
@@ -1595,6 +1705,10 @@
       <c r="H25" s="47" t="n"/>
       <c r="I25" s="47" t="n"/>
       <c r="J25" s="47" t="n"/>
+      <c r="L25" s="65">
+        <f>IF(B25="","",AVERAGE($F$10:$F$28))</f>
+        <v/>
+      </c>
     </row>
     <row r="26" ht="30" customHeight="1" s="30">
       <c r="A26" s="46" t="n">
@@ -1609,6 +1723,10 @@
       <c r="H26" s="47" t="n"/>
       <c r="I26" s="47" t="n"/>
       <c r="J26" s="47" t="n"/>
+      <c r="L26" s="65">
+        <f>IF(B26="","",AVERAGE($F$10:$F$28))</f>
+        <v/>
+      </c>
     </row>
     <row r="27" ht="30" customHeight="1" s="30">
       <c r="A27" s="46" t="n">
@@ -1623,6 +1741,10 @@
       <c r="H27" s="47" t="n"/>
       <c r="I27" s="47" t="n"/>
       <c r="J27" s="47" t="n"/>
+      <c r="L27" s="65">
+        <f>IF(B27="","",AVERAGE($F$10:$F$28))</f>
+        <v/>
+      </c>
     </row>
     <row r="28" ht="30" customHeight="1" s="30">
       <c r="A28" s="46" t="n">
@@ -1637,6 +1759,10 @@
       <c r="H28" s="47" t="n"/>
       <c r="I28" s="47" t="n"/>
       <c r="J28" s="47" t="n"/>
+      <c r="L28" s="65">
+        <f>IF(B28="","",AVERAGE($F$10:$F$28))</f>
+        <v/>
+      </c>
     </row>
     <row r="30" ht="19.5" customHeight="1" s="30">
       <c r="A30" s="38" t="inlineStr">

--- a/templates/10-value-stream-map.xlsx
+++ b/templates/10-value-stream-map.xlsx
@@ -697,7 +697,7 @@
     <from>
       <col>13</col>
       <colOff>0</colOff>
-      <row>8</row>
+      <row>2</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7920000" cy="3240000"/>
@@ -1060,6 +1060,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="19.5" customHeight="1" s="30">
       <c r="A4" s="38" t="inlineStr">
         <is>
@@ -1103,6 +1104,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9" ht="31.5" customHeight="1" s="30">
       <c r="A9" s="43" t="inlineStr">
         <is>
@@ -1764,6 +1766,7 @@
         <v/>
       </c>
     </row>
+    <row r="29"/>
     <row r="30" ht="19.5" customHeight="1" s="30">
       <c r="A30" s="38" t="inlineStr">
         <is>
@@ -1878,6 +1881,7 @@
       </c>
       <c r="E40" s="55" t="n"/>
     </row>
+    <row r="41"/>
     <row r="42" ht="19.5" customHeight="1" s="30">
       <c r="A42" s="38" t="inlineStr">
         <is>

--- a/templates/10-value-stream-map.xlsx
+++ b/templates/10-value-stream-map.xlsx
@@ -650,8 +650,8 @@
         <tickLblPos val="low"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="3"/>
-        <tickMarkSkip val="3"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>

--- a/templates/10-value-stream-map.xlsx
+++ b/templates/10-value-stream-map.xlsx
@@ -21,7 +21,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -163,6 +163,11 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF6B7280"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -258,7 +263,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -451,6 +456,13 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1031,7 +1043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L49"/>
+  <dimension ref="A1:L50"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -1921,19 +1933,29 @@
       <c r="I43" s="43" t="n"/>
       <c r="J43" s="43" t="n"/>
     </row>
-    <row r="44" ht="15" customHeight="1" s="30">
+    <row r="44" ht="44" customHeight="1" s="30">
       <c r="A44" s="56" t="inlineStr">
         <is>
           <t>Awaiting customer reply</t>
         </is>
       </c>
-      <c r="B44" s="57" t="n"/>
+      <c r="B44" s="66" t="n">
+        <v>960</v>
+      </c>
       <c r="C44" s="58">
         <f>IFERROR(B44/$E$33,"")</f>
         <v/>
       </c>
-      <c r="D44" s="57" t="n"/>
-      <c r="E44" s="57" t="n"/>
+      <c r="D44" s="67" t="inlineStr">
+        <is>
+          <t>Nobody — the case sits until the customer replies</t>
+        </is>
+      </c>
+      <c r="E44" s="67" t="inlineStr">
+        <is>
+          <t>One email goes out and no reminder ever follows. The clock is not paused, so this wait is the single largest block of lead time in the whole stream.</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="30">
       <c r="A45" s="56" t="inlineStr">
@@ -2004,6 +2026,13 @@
       </c>
       <c r="D49" s="57" t="n"/>
       <c r="E49" s="57" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="68" t="inlineStr">
+        <is>
+          <t>How to fill this block. Take the minutes from the same extract that produced the step table above — the median, not the mean, because a handful of week-long waits will otherwise set your whole plan. OWNER is whoever can shorten it; if the honest answer is nobody, write that, because an unowned wait is the finding. WHY DOES IT WAIT should name the mechanism, not the symptom: 'no reminder is sent' is actionable, 'the customer is slow' is not. Row 44 is a worked example.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="18">

--- a/templates/10-value-stream-map.xlsx
+++ b/templates/10-value-stream-map.xlsx
@@ -1599,7 +1599,7 @@
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" s="30">
-      <c r="A19" s="46" t="n">
+      <c r="A19" s="61" t="n">
         <v>10</v>
       </c>
       <c r="B19" s="47" t="n"/>
@@ -1617,7 +1617,7 @@
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" s="30">
-      <c r="A20" s="46" t="n">
+      <c r="A20" s="61" t="n">
         <v>11</v>
       </c>
       <c r="B20" s="47" t="n"/>
@@ -1635,7 +1635,7 @@
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" s="30">
-      <c r="A21" s="46" t="n">
+      <c r="A21" s="61" t="n">
         <v>12</v>
       </c>
       <c r="B21" s="47" t="n"/>
@@ -1653,7 +1653,7 @@
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" s="30">
-      <c r="A22" s="46" t="n">
+      <c r="A22" s="61" t="n">
         <v>13</v>
       </c>
       <c r="B22" s="47" t="n"/>
@@ -1671,7 +1671,7 @@
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" s="30">
-      <c r="A23" s="46" t="n">
+      <c r="A23" s="61" t="n">
         <v>14</v>
       </c>
       <c r="B23" s="47" t="n"/>
@@ -1689,7 +1689,7 @@
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" s="30">
-      <c r="A24" s="46" t="n">
+      <c r="A24" s="61" t="n">
         <v>15</v>
       </c>
       <c r="B24" s="47" t="n"/>
@@ -1707,7 +1707,7 @@
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" s="30">
-      <c r="A25" s="46" t="n">
+      <c r="A25" s="61" t="n">
         <v>16</v>
       </c>
       <c r="B25" s="47" t="n"/>
@@ -1725,7 +1725,7 @@
       </c>
     </row>
     <row r="26" ht="30" customHeight="1" s="30">
-      <c r="A26" s="46" t="n">
+      <c r="A26" s="61" t="n">
         <v>17</v>
       </c>
       <c r="B26" s="47" t="n"/>
@@ -1743,7 +1743,7 @@
       </c>
     </row>
     <row r="27" ht="30" customHeight="1" s="30">
-      <c r="A27" s="46" t="n">
+      <c r="A27" s="61" t="n">
         <v>18</v>
       </c>
       <c r="B27" s="47" t="n"/>
@@ -1761,7 +1761,7 @@
       </c>
     </row>
     <row r="28" ht="30" customHeight="1" s="30">
-      <c r="A28" s="46" t="n">
+      <c r="A28" s="61" t="n">
         <v>19</v>
       </c>
       <c r="B28" s="47" t="n"/>

--- a/templates/10-value-stream-map.xlsx
+++ b/templates/10-value-stream-map.xlsx
@@ -169,7 +169,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -228,6 +228,11 @@
         <fgColor rgb="FFF2F7FF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF9E3"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -263,7 +268,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -463,6 +468,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1599,7 +1607,7 @@
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" s="30">
-      <c r="A19" s="61" t="n">
+      <c r="A19" s="69" t="n">
         <v>10</v>
       </c>
       <c r="B19" s="47" t="n"/>
@@ -1617,7 +1625,7 @@
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" s="30">
-      <c r="A20" s="61" t="n">
+      <c r="A20" s="69" t="n">
         <v>11</v>
       </c>
       <c r="B20" s="47" t="n"/>
@@ -1635,7 +1643,7 @@
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" s="30">
-      <c r="A21" s="61" t="n">
+      <c r="A21" s="69" t="n">
         <v>12</v>
       </c>
       <c r="B21" s="47" t="n"/>
@@ -1653,7 +1661,7 @@
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" s="30">
-      <c r="A22" s="61" t="n">
+      <c r="A22" s="69" t="n">
         <v>13</v>
       </c>
       <c r="B22" s="47" t="n"/>
@@ -1671,7 +1679,7 @@
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" s="30">
-      <c r="A23" s="61" t="n">
+      <c r="A23" s="69" t="n">
         <v>14</v>
       </c>
       <c r="B23" s="47" t="n"/>
@@ -1689,7 +1697,7 @@
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" s="30">
-      <c r="A24" s="61" t="n">
+      <c r="A24" s="69" t="n">
         <v>15</v>
       </c>
       <c r="B24" s="47" t="n"/>
@@ -1707,7 +1715,7 @@
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" s="30">
-      <c r="A25" s="61" t="n">
+      <c r="A25" s="69" t="n">
         <v>16</v>
       </c>
       <c r="B25" s="47" t="n"/>
@@ -1725,7 +1733,7 @@
       </c>
     </row>
     <row r="26" ht="30" customHeight="1" s="30">
-      <c r="A26" s="61" t="n">
+      <c r="A26" s="69" t="n">
         <v>17</v>
       </c>
       <c r="B26" s="47" t="n"/>
@@ -1743,7 +1751,7 @@
       </c>
     </row>
     <row r="27" ht="30" customHeight="1" s="30">
-      <c r="A27" s="61" t="n">
+      <c r="A27" s="69" t="n">
         <v>18</v>
       </c>
       <c r="B27" s="47" t="n"/>
@@ -1761,7 +1769,7 @@
       </c>
     </row>
     <row r="28" ht="30" customHeight="1" s="30">
-      <c r="A28" s="61" t="n">
+      <c r="A28" s="69" t="n">
         <v>19</v>
       </c>
       <c r="B28" s="47" t="n"/>

--- a/templates/10-value-stream-map.xlsx
+++ b/templates/10-value-stream-map.xlsx
@@ -1607,7 +1607,7 @@
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" s="30">
-      <c r="A19" s="69" t="n">
+      <c r="A19" s="61" t="n">
         <v>10</v>
       </c>
       <c r="B19" s="47" t="n"/>
@@ -1625,7 +1625,7 @@
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" s="30">
-      <c r="A20" s="69" t="n">
+      <c r="A20" s="61" t="n">
         <v>11</v>
       </c>
       <c r="B20" s="47" t="n"/>
@@ -1643,7 +1643,7 @@
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" s="30">
-      <c r="A21" s="69" t="n">
+      <c r="A21" s="61" t="n">
         <v>12</v>
       </c>
       <c r="B21" s="47" t="n"/>
@@ -1661,7 +1661,7 @@
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" s="30">
-      <c r="A22" s="69" t="n">
+      <c r="A22" s="61" t="n">
         <v>13</v>
       </c>
       <c r="B22" s="47" t="n"/>
@@ -1679,7 +1679,7 @@
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" s="30">
-      <c r="A23" s="69" t="n">
+      <c r="A23" s="61" t="n">
         <v>14</v>
       </c>
       <c r="B23" s="47" t="n"/>
@@ -1697,7 +1697,7 @@
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" s="30">
-      <c r="A24" s="69" t="n">
+      <c r="A24" s="61" t="n">
         <v>15</v>
       </c>
       <c r="B24" s="47" t="n"/>
@@ -1715,7 +1715,7 @@
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" s="30">
-      <c r="A25" s="69" t="n">
+      <c r="A25" s="61" t="n">
         <v>16</v>
       </c>
       <c r="B25" s="47" t="n"/>
@@ -1733,7 +1733,7 @@
       </c>
     </row>
     <row r="26" ht="30" customHeight="1" s="30">
-      <c r="A26" s="69" t="n">
+      <c r="A26" s="61" t="n">
         <v>17</v>
       </c>
       <c r="B26" s="47" t="n"/>
@@ -1751,7 +1751,7 @@
       </c>
     </row>
     <row r="27" ht="30" customHeight="1" s="30">
-      <c r="A27" s="69" t="n">
+      <c r="A27" s="61" t="n">
         <v>18</v>
       </c>
       <c r="B27" s="47" t="n"/>
@@ -1769,7 +1769,7 @@
       </c>
     </row>
     <row r="28" ht="30" customHeight="1" s="30">
-      <c r="A28" s="69" t="n">
+      <c r="A28" s="61" t="n">
         <v>19</v>
       </c>
       <c r="B28" s="47" t="n"/>

--- a/templates/10-value-stream-map.xlsx
+++ b/templates/10-value-stream-map.xlsx
@@ -268,7 +268,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -470,6 +470,24 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="15" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1115,12 +1133,12 @@
     <row r="7" ht="15" customHeight="1" s="30">
       <c r="A7" s="42" t="inlineStr">
         <is>
-          <t>Row 1 example</t>
+          <t>Green cells</t>
         </is>
       </c>
       <c r="B7" s="40" t="inlineStr">
         <is>
-          <t>A realistic worked example, so you can see the expected format. Delete or overwrite it.</t>
+          <t>A realistic worked example, so you can see the expected format and the sheet is not blank when you open it. Replace it with your own.</t>
         </is>
       </c>
     </row>
@@ -1508,7 +1526,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J16" s="62" t="inlineStr"/>
+      <c r="J16" s="72" t="inlineStr"/>
       <c r="L16" s="65">
         <f>IF(B16="","",AVERAGE($F$10:$F$28))</f>
         <v/>
@@ -1600,14 +1618,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J18" s="62" t="inlineStr"/>
+      <c r="J18" s="72" t="inlineStr"/>
       <c r="L18" s="65">
         <f>IF(B18="","",AVERAGE($F$10:$F$28))</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" s="30">
-      <c r="A19" s="61" t="n">
+      <c r="A19" s="69" t="n">
         <v>10</v>
       </c>
       <c r="B19" s="47" t="n"/>
@@ -1625,7 +1643,7 @@
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" s="30">
-      <c r="A20" s="61" t="n">
+      <c r="A20" s="69" t="n">
         <v>11</v>
       </c>
       <c r="B20" s="47" t="n"/>
@@ -1643,7 +1661,7 @@
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" s="30">
-      <c r="A21" s="61" t="n">
+      <c r="A21" s="69" t="n">
         <v>12</v>
       </c>
       <c r="B21" s="47" t="n"/>
@@ -1661,7 +1679,7 @@
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" s="30">
-      <c r="A22" s="61" t="n">
+      <c r="A22" s="69" t="n">
         <v>13</v>
       </c>
       <c r="B22" s="47" t="n"/>
@@ -1679,7 +1697,7 @@
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" s="30">
-      <c r="A23" s="61" t="n">
+      <c r="A23" s="69" t="n">
         <v>14</v>
       </c>
       <c r="B23" s="47" t="n"/>
@@ -1697,7 +1715,7 @@
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" s="30">
-      <c r="A24" s="61" t="n">
+      <c r="A24" s="69" t="n">
         <v>15</v>
       </c>
       <c r="B24" s="47" t="n"/>
@@ -1715,7 +1733,7 @@
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" s="30">
-      <c r="A25" s="61" t="n">
+      <c r="A25" s="69" t="n">
         <v>16</v>
       </c>
       <c r="B25" s="47" t="n"/>
@@ -1733,7 +1751,7 @@
       </c>
     </row>
     <row r="26" ht="30" customHeight="1" s="30">
-      <c r="A26" s="61" t="n">
+      <c r="A26" s="69" t="n">
         <v>17</v>
       </c>
       <c r="B26" s="47" t="n"/>
@@ -1751,7 +1769,7 @@
       </c>
     </row>
     <row r="27" ht="30" customHeight="1" s="30">
-      <c r="A27" s="61" t="n">
+      <c r="A27" s="69" t="n">
         <v>18</v>
       </c>
       <c r="B27" s="47" t="n"/>
@@ -1769,7 +1787,7 @@
       </c>
     </row>
     <row r="28" ht="30" customHeight="1" s="30">
-      <c r="A28" s="61" t="n">
+      <c r="A28" s="69" t="n">
         <v>19</v>
       </c>
       <c r="B28" s="47" t="n"/>

--- a/templates/10-value-stream-map.xlsx
+++ b/templates/10-value-stream-map.xlsx
@@ -268,7 +268,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -487,6 +487,9 @@
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1082,6 +1085,8 @@
     <col width="15" customWidth="1" style="30" min="8" max="8"/>
     <col width="11" customWidth="1" style="30" min="9" max="9"/>
     <col width="34" customWidth="1" style="30" min="10" max="10"/>
+    <col width="13" customWidth="1" style="30" min="11" max="11"/>
+    <col width="13" customWidth="1" style="30" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1" s="30">
@@ -2053,33 +2058,34 @@
       <c r="D49" s="57" t="n"/>
       <c r="E49" s="57" t="n"/>
     </row>
-    <row r="50">
-      <c r="A50" s="68" t="inlineStr">
+    <row r="50" ht="39" customHeight="1" s="30">
+      <c r="A50" s="76" t="inlineStr">
         <is>
           <t>How to fill this block. Take the minutes from the same extract that produced the step table above — the median, not the mean, because a handful of week-long waits will otherwise set your whole plan. OWNER is whoever can shorten it; if the honest answer is nobody, write that, because an unowned wait is the finding. WHY DOES IT WAIT should name the mechanism, not the symptom: 'no reminder is sent' is actionable, 'the customer is slow' is not. Row 44 is a worked example.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A37:D37"/>
+  <mergeCells count="19">
     <mergeCell ref="B7:F7"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="A34:D34"/>
     <mergeCell ref="A35:D35"/>
     <mergeCell ref="A38:D38"/>
-    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="A50:L50"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A34:D34"/>
     <mergeCell ref="A30:J30"/>
     <mergeCell ref="A39:D39"/>
     <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="A33:D33"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A33:D33"/>
     <mergeCell ref="A42:J42"/>
     <mergeCell ref="A32:D32"/>
-    <mergeCell ref="A36:D36"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="H10:H28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">

--- a/templates/10-value-stream-map.xlsx
+++ b/templates/10-value-stream-map.xlsx
@@ -234,7 +234,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -257,6 +257,50 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD8DEE8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD8DEE8"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD8DEE8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD8DEE8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD8DEE8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD8DEE8"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD8DEE8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD8DEE8"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -268,7 +312,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -492,6 +536,8 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1987,6 +2033,13 @@
           <t>One email goes out and no reminder ever follows. The clock is not paused, so this wait is the single largest block of lead time in the whole stream.</t>
         </is>
       </c>
+      <c r="F44" s="77" t="n"/>
+      <c r="G44" s="77" t="n"/>
+      <c r="H44" s="77" t="n"/>
+      <c r="I44" s="77" t="n"/>
+      <c r="J44" s="77" t="n"/>
+      <c r="K44" s="77" t="n"/>
+      <c r="L44" s="78" t="n"/>
     </row>
     <row r="45" ht="15" customHeight="1" s="30">
       <c r="A45" s="56" t="inlineStr">
@@ -2066,13 +2119,14 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="20">
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="A35:D35"/>
     <mergeCell ref="A38:D38"/>
     <mergeCell ref="A50:L50"/>
     <mergeCell ref="A40:D40"/>
     <mergeCell ref="A31:D31"/>
+    <mergeCell ref="E44:L44"/>
     <mergeCell ref="A34:D34"/>
     <mergeCell ref="A30:J30"/>
     <mergeCell ref="A39:D39"/>

--- a/templates/10-value-stream-map.xlsx
+++ b/templates/10-value-stream-map.xlsx
@@ -312,7 +312,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -538,6 +538,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1193,7 +1199,13 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
+    <row r="8" ht="36" customHeight="1" s="30">
+      <c r="A8" s="79" t="inlineStr">
+        <is>
+          <t>Key: Touch time = minutes anyone is actually working on the contact at that step, not the minutes it sits at that step. The whole map totals 26 minutes of touch inside 2,426 minutes of lead time (E31, E33) — 1.07% (E35). That ratio is the point of the map: the waste is almost never in the working</t>
+        </is>
+      </c>
+    </row>
     <row r="9" ht="31.5" customHeight="1" s="30">
       <c r="A9" s="43" t="inlineStr">
         <is>
@@ -1971,10 +1983,10 @@
       <c r="E40" s="55" t="n"/>
     </row>
     <row r="41"/>
-    <row r="42" ht="19.5" customHeight="1" s="30">
-      <c r="A42" s="38" t="inlineStr">
-        <is>
-          <t>WAITING STATES  —  rank them. The biggest one is your project.</t>
+    <row r="42" ht="36" customHeight="1" s="30">
+      <c r="A42" s="80" t="inlineStr">
+        <is>
+          <t>WAITING STATES  —  rank them. The biggest one is your project.  ·  Key: % of lead time = that wait as a percentage of the whole door-to-door lead time, 2,426 minutes here (E33), not of the total waiting. Measuring each wait against the other waits makes every one look large and tells you nothing about which to remove</t>
         </is>
       </c>
     </row>
@@ -2119,8 +2131,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="21">
     <mergeCell ref="B7:F7"/>
+    <mergeCell ref="A8:J8"/>
     <mergeCell ref="A35:D35"/>
     <mergeCell ref="A38:D38"/>
     <mergeCell ref="A50:L50"/>

--- a/templates/10-value-stream-map.xlsx
+++ b/templates/10-value-stream-map.xlsx
@@ -1199,10 +1199,12 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="36" customHeight="1" s="30">
+    <row r="8" ht="84" customHeight="1" s="30">
       <c r="A8" s="79" t="inlineStr">
         <is>
-          <t>Key: Touch time = minutes anyone is actually working on the contact at that step, not the minutes it sits at that step. The whole map totals 26 minutes of touch inside 2,426 minutes of lead time (E31, E33) — 1.07% (E35). That ratio is the point of the map: the waste is almost never in the working</t>
+          <t xml:space="preserve">  ·  Key:
+• Touch time = minutes anyone is actually working on the contact at that step, not the minutes it sits at that step. The whole map totals 26 minutes of touch inside 2,426 minutes of lead time (E31, E33) — 1.07% (E35). That ratio is the point of the map: the waste is almost never in the working  ·  Key:
+• Touch time = minutes anyone is actually working on the contact at that step, not the minutes it sits at that step. The whole map totals 26 minutes of touch inside 2,426 minutes of lead time (E31, E33) — 1.07% (E35). That ratio is the point of the map: the waste is almost never in the working</t>
         </is>
       </c>
     </row>
@@ -1983,10 +1985,12 @@
       <c r="E40" s="55" t="n"/>
     </row>
     <row r="41"/>
-    <row r="42" ht="36" customHeight="1" s="30">
+    <row r="42" ht="84" customHeight="1" s="30">
       <c r="A42" s="80" t="inlineStr">
         <is>
-          <t>WAITING STATES  —  rank them. The biggest one is your project.  ·  Key: % of lead time = that wait as a percentage of the whole door-to-door lead time, 2,426 minutes here (E33), not of the total waiting. Measuring each wait against the other waits makes every one look large and tells you nothing about which to remove</t>
+          <t>WAITING STATES  —  rank them. The biggest one is your project.  ·  Key:
+• % of lead time = that wait as a percentage of the whole door-to-door lead time, 2,426 minutes here (E33), not of the total waiting. Measuring each wait against the other waits makes every one look large and tells you nothing about which to remove  ·  Key:
+• % of lead time = that wait as a percentage of the whole door-to-door lead time, 2,426 minutes here (E33), not of the total waiting. Measuring each wait against the other waits makes every one look large and tells you nothing about which to remove</t>
         </is>
       </c>
     </row>

--- a/templates/10-value-stream-map.xlsx
+++ b/templates/10-value-stream-map.xlsx
@@ -21,7 +21,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -168,6 +168,11 @@
       <color rgb="FF6B7280"/>
       <sz val="9"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF4B5563"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -312,7 +317,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -543,6 +548,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -788,7 +796,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>13</col>
+      <col>15</col>
       <colOff>0</colOff>
       <row>2</row>
       <rowOff>0</rowOff>
@@ -1124,7 +1132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L50"/>
+  <dimension ref="A1:V50"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -1139,6 +1147,15 @@
     <col width="34" customWidth="1" style="30" min="10" max="10"/>
     <col width="13" customWidth="1" style="30" min="11" max="11"/>
     <col width="13" customWidth="1" style="30" min="12" max="12"/>
+    <col width="13" customWidth="1" style="30" min="14" max="14"/>
+    <col width="13" customWidth="1" style="30" min="15" max="15"/>
+    <col width="13" customWidth="1" style="30" min="16" max="16"/>
+    <col width="13" customWidth="1" style="30" min="17" max="17"/>
+    <col width="13" customWidth="1" style="30" min="18" max="18"/>
+    <col width="13" customWidth="1" style="30" min="19" max="19"/>
+    <col width="13" customWidth="1" style="30" min="20" max="20"/>
+    <col width="13" customWidth="1" style="30" min="21" max="21"/>
+    <col width="13" customWidth="1" style="30" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1" s="30">
@@ -1199,10 +1216,12 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="84" customHeight="1" s="30">
+    <row r="8" ht="156" customHeight="1" s="30">
       <c r="A8" s="79" t="inlineStr">
         <is>
           <t xml:space="preserve">  ·  Key:
+• Touch time = minutes anyone is actually working on the contact at that step, not the minutes it sits at that step. The whole map totals 26 minutes of touch inside 2,426 minutes of lead time (E31, E33) — 1.07% (E35). That ratio is the point of the map: the waste is almost never in the working  ·  Key:
+• Touch time = minutes anyone is actually working on the contact at that step, not the minutes it sits at that step. The whole map totals 26 minutes of touch inside 2,426 minutes of lead time (E31, E33) — 1.07% (E35). That ratio is the point of the map: the waste is almost never in the working  ·  Key:
 • Touch time = minutes anyone is actually working on the contact at that step, not the minutes it sits at that step. The whole map totals 26 minutes of touch inside 2,426 minutes of lead time (E31, E33) — 1.07% (E35). That ratio is the point of the map: the waste is almost never in the working  ·  Key:
 • Touch time = minutes anyone is actually working on the contact at that step, not the minutes it sits at that step. The whole map totals 26 minutes of touch inside 2,426 minutes of lead time (E31, E33) — 1.07% (E35). That ratio is the point of the map: the waste is almost never in the working</t>
         </is>
@@ -1869,7 +1888,14 @@
         <v/>
       </c>
     </row>
-    <row r="29"/>
+    <row r="29" ht="66" customHeight="1" s="30">
+      <c r="N29" s="81" t="inlineStr">
+        <is>
+          <t>HOW TO READ IT.  Working time and waiting time on the same axis, one pair per step. The worked example totals 26 minutes of touch inside 2,426 minutes of lead time — 1.07%. What should worry you is a tall wait bar next to a step nobody owns: that is the queue to attack, and it is almost never the step people expect.
+SO:  Attack the waiting, not the working. At 1.07% efficiency, halving every touch time on the map would save 13 minutes of 2,426 — the queues are the project.</t>
+        </is>
+      </c>
+    </row>
     <row r="30" ht="19.5" customHeight="1" s="30">
       <c r="A30" s="38" t="inlineStr">
         <is>
@@ -1985,10 +2011,12 @@
       <c r="E40" s="55" t="n"/>
     </row>
     <row r="41"/>
-    <row r="42" ht="84" customHeight="1" s="30">
+    <row r="42" ht="156" customHeight="1" s="30">
       <c r="A42" s="80" t="inlineStr">
         <is>
           <t>WAITING STATES  —  rank them. The biggest one is your project.  ·  Key:
+• % of lead time = that wait as a percentage of the whole door-to-door lead time, 2,426 minutes here (E33), not of the total waiting. Measuring each wait against the other waits makes every one look large and tells you nothing about which to remove  ·  Key:
+• % of lead time = that wait as a percentage of the whole door-to-door lead time, 2,426 minutes here (E33), not of the total waiting. Measuring each wait against the other waits makes every one look large and tells you nothing about which to remove  ·  Key:
 • % of lead time = that wait as a percentage of the whole door-to-door lead time, 2,426 minutes here (E33), not of the total waiting. Measuring each wait against the other waits makes every one look large and tells you nothing about which to remove  ·  Key:
 • % of lead time = that wait as a percentage of the whole door-to-door lead time, 2,426 minutes here (E33), not of the total waiting. Measuring each wait against the other waits makes every one look large and tells you nothing about which to remove</t>
         </is>
@@ -2135,13 +2163,14 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="22">
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="A8:J8"/>
     <mergeCell ref="A35:D35"/>
     <mergeCell ref="A38:D38"/>
     <mergeCell ref="A50:L50"/>
     <mergeCell ref="A40:D40"/>
+    <mergeCell ref="N29:V29"/>
     <mergeCell ref="A31:D31"/>
     <mergeCell ref="E44:L44"/>
     <mergeCell ref="A34:D34"/>

--- a/templates/10-value-stream-map.xlsx
+++ b/templates/10-value-stream-map.xlsx
@@ -1216,13 +1216,10 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="156" customHeight="1" s="30">
+    <row r="8" ht="48" customHeight="1" s="30">
       <c r="A8" s="79" t="inlineStr">
         <is>
           <t xml:space="preserve">  ·  Key:
-• Touch time = minutes anyone is actually working on the contact at that step, not the minutes it sits at that step. The whole map totals 26 minutes of touch inside 2,426 minutes of lead time (E31, E33) — 1.07% (E35). That ratio is the point of the map: the waste is almost never in the working  ·  Key:
-• Touch time = minutes anyone is actually working on the contact at that step, not the minutes it sits at that step. The whole map totals 26 minutes of touch inside 2,426 minutes of lead time (E31, E33) — 1.07% (E35). That ratio is the point of the map: the waste is almost never in the working  ·  Key:
-• Touch time = minutes anyone is actually working on the contact at that step, not the minutes it sits at that step. The whole map totals 26 minutes of touch inside 2,426 minutes of lead time (E31, E33) — 1.07% (E35). That ratio is the point of the map: the waste is almost never in the working  ·  Key:
 • Touch time = minutes anyone is actually working on the contact at that step, not the minutes it sits at that step. The whole map totals 26 minutes of touch inside 2,426 minutes of lead time (E31, E33) — 1.07% (E35). That ratio is the point of the map: the waste is almost never in the working</t>
         </is>
       </c>
@@ -2011,13 +2008,10 @@
       <c r="E40" s="55" t="n"/>
     </row>
     <row r="41"/>
-    <row r="42" ht="156" customHeight="1" s="30">
+    <row r="42" ht="48" customHeight="1" s="30">
       <c r="A42" s="80" t="inlineStr">
         <is>
           <t>WAITING STATES  —  rank them. The biggest one is your project.  ·  Key:
-• % of lead time = that wait as a percentage of the whole door-to-door lead time, 2,426 minutes here (E33), not of the total waiting. Measuring each wait against the other waits makes every one look large and tells you nothing about which to remove  ·  Key:
-• % of lead time = that wait as a percentage of the whole door-to-door lead time, 2,426 minutes here (E33), not of the total waiting. Measuring each wait against the other waits makes every one look large and tells you nothing about which to remove  ·  Key:
-• % of lead time = that wait as a percentage of the whole door-to-door lead time, 2,426 minutes here (E33), not of the total waiting. Measuring each wait against the other waits makes every one look large and tells you nothing about which to remove  ·  Key:
 • % of lead time = that wait as a percentage of the whole door-to-door lead time, 2,426 minutes here (E33), not of the total waiting. Measuring each wait against the other waits makes every one look large and tells you nothing about which to remove</t>
         </is>
       </c>

--- a/templates/10-value-stream-map.xlsx
+++ b/templates/10-value-stream-map.xlsx
@@ -317,7 +317,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -550,6 +550,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1097,9 +1100,27 @@
     </row>
     <row r="17"/>
     <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
+    <row r="19" ht="26" customHeight="1" s="30">
+      <c r="A19" s="82" t="inlineStr">
+        <is>
+          <t>WHAT THE COLUMNS MEAN — the short version sits above each table; this is the same thing with the worked example</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="44" customHeight="1" s="30">
+      <c r="A20" s="81" t="inlineStr">
+        <is>
+          <t>Touch time = minutes anyone is actually working on the contact at that step, not the minutes it sits at that step. The whole map totals 26 minutes of touch inside 2,426 minutes of lead time (E31, E33) — 1.07% (E35). That ratio is the point of the map: the waste is almost never in the working</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="39" customHeight="1" s="30">
+      <c r="A21" s="81" t="inlineStr">
+        <is>
+          <t>% of lead time = that wait as a percentage of the whole door-to-door lead time, 2,426 minutes here (E33), not of the total waiting. Measuring each wait against the other waits makes every one look large and tells you nothing about which to remove</t>
+        </is>
+      </c>
+    </row>
     <row r="22"/>
     <row r="23"/>
     <row r="24"/>
@@ -1120,6 +1141,11 @@
     <row r="39"/>
     <row r="40"/>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A19:B19"/>
+  </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1216,11 +1242,11 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="48" customHeight="1" s="30">
+    <row r="8" ht="36" customHeight="1" s="30">
       <c r="A8" s="79" t="inlineStr">
         <is>
           <t xml:space="preserve">  ·  Key:
-• Touch time = minutes anyone is actually working on the contact at that step, not the minutes it sits at that step. The whole map totals 26 minutes of touch inside 2,426 minutes of lead time (E31, E33) — 1.07% (E35). That ratio is the point of the map: the waste is almost never in the working</t>
+• Touch time = minutes anyone is actually working on the contact at that step, not the minutes it sits at that step.</t>
         </is>
       </c>
     </row>
@@ -2008,11 +2034,11 @@
       <c r="E40" s="55" t="n"/>
     </row>
     <row r="41"/>
-    <row r="42" ht="48" customHeight="1" s="30">
+    <row r="42" ht="36" customHeight="1" s="30">
       <c r="A42" s="80" t="inlineStr">
         <is>
           <t>WAITING STATES  —  rank them. The biggest one is your project.  ·  Key:
-• % of lead time = that wait as a percentage of the whole door-to-door lead time, 2,426 minutes here (E33), not of the total waiting. Measuring each wait against the other waits makes every one look large and tells you nothing about which to remove</t>
+• % of lead time = that wait as a percentage of the whole door-to-door lead time, 2,426 minutes here (E33), not of the total waiting.</t>
         </is>
       </c>
     </row>

--- a/templates/10-value-stream-map.xlsx
+++ b/templates/10-value-stream-map.xlsx
@@ -1142,8 +1142,8 @@
     <row r="40"/>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A20:B20"/>
     <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A20:B20"/>
     <mergeCell ref="A19:B19"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>

--- a/templates/10-value-stream-map.xlsx
+++ b/templates/10-value-stream-map.xlsx
@@ -1283,7 +1283,7 @@
       </c>
       <c r="G9" s="43" t="inlineStr">
         <is>
-          <t>% complete &amp;amp; accurate</t>
+          <t>% complete &amp; accurate</t>
         </is>
       </c>
       <c r="H9" s="43" t="inlineStr">
